--- a/artfynd/A 43397-2026 artfynd.xlsx
+++ b/artfynd/A 43397-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137480010</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137480012</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137480020</v>
       </c>
       <c r="B4" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137479972</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137479995</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137480007</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137480029</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137479964</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137479970</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137479977</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137479979</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>137479988</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>137480001</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>137480016</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137479966</v>
       </c>
       <c r="B16" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>137480018</v>
       </c>
       <c r="B17" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>137479968</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>137479975</v>
       </c>
       <c r="B19" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>137479981</v>
       </c>
       <c r="B20" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>137479984</v>
       </c>
       <c r="B21" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>137479990</v>
       </c>
       <c r="B22" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>137479993</v>
       </c>
       <c r="B23" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>137479999</v>
       </c>
       <c r="B24" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3315,7 +3315,7 @@
         <v>137480005</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>137480014</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>137480022</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>137480025</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137480027</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>137480031</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>137480033</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
